--- a/data/trans_dic/P1416-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1416-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,8</t>
+          <t>6,13; 10,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,31</t>
+          <t>6,14; 11,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 13,92</t>
+          <t>7,57; 13,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 24,57</t>
+          <t>9,19; 20,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,83; 14,47</t>
+          <t>8,78; 14,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 12,12</t>
+          <t>6,51; 11,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,62</t>
+          <t>7,03; 13,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 15,4</t>
+          <t>6,82; 16,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,16; 11,66</t>
+          <t>7,75; 11,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 10,72</t>
+          <t>6,97; 10,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 12,0</t>
+          <t>8,03; 11,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,96; 18,65</t>
+          <t>9,34; 16,51</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,62</t>
+          <t>6,38; 10,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,72</t>
+          <t>4,72; 8,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,52</t>
+          <t>4,67; 8,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 15,89</t>
+          <t>7,86; 14,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,26; 13,66</t>
+          <t>8,25; 13,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 11,0</t>
+          <t>6,37; 11,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,23</t>
+          <t>7,52; 12,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 15,48</t>
+          <t>10,27; 16,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,11</t>
+          <t>7,81; 11,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 8,84</t>
+          <t>6,04; 8,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,71</t>
+          <t>6,74; 10,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 14,51</t>
+          <t>10,19; 14,91</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,0</t>
+          <t>4,59; 8,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,4</t>
+          <t>4,5; 8,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,85</t>
+          <t>3,31; 6,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 14,65</t>
+          <t>8,87; 14,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 13,45</t>
+          <t>8,53; 13,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,5</t>
+          <t>8,74; 13,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,46</t>
+          <t>7,77; 12,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 13,61</t>
+          <t>9,64; 13,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,63</t>
+          <t>7,28; 10,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,18</t>
+          <t>7,08; 10,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,98</t>
+          <t>5,82; 8,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,78; 13,31</t>
+          <t>9,75; 13,18</t>
         </is>
       </c>
     </row>
@@ -1084,34 +1084,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15,03%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>7,63%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>4,3%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,66</t>
+          <t>3,49; 8,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,27</t>
+          <t>1,36; 4,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,07</t>
+          <t>2,06; 5,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,54</t>
+          <t>8,11; 13,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 13,06</t>
+          <t>7,42; 12,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,65</t>
+          <t>4,19; 8,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,06</t>
+          <t>5,57; 9,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 16,49</t>
+          <t>12,93; 17,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,62</t>
+          <t>6,1; 9,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,63</t>
+          <t>3,2; 5,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,93</t>
+          <t>4,37; 6,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,96</t>
+          <t>11,24; 14,47</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,37; 9,42</t>
+          <t>4,2; 9,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,53</t>
+          <t>1,97; 5,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,25</t>
+          <t>2,3; 6,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,11</t>
+          <t>6,21; 10,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,37</t>
+          <t>4,84; 10,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,79</t>
+          <t>2,8; 6,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 10,91</t>
+          <t>5,57; 10,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,07; 14,23</t>
+          <t>10,04; 14,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,85</t>
+          <t>5,23; 8,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,5</t>
+          <t>2,75; 5,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,83</t>
+          <t>4,43; 7,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,52</t>
+          <t>8,77; 11,75</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,76; 7,91</t>
+          <t>2,49; 7,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,2</t>
+          <t>1,94; 7,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,14</t>
+          <t>0,54; 3,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,74</t>
+          <t>4,08; 8,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 13,36</t>
+          <t>7,21; 13,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,8</t>
+          <t>2,49; 6,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,77</t>
+          <t>2,12; 6,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 10,42</t>
+          <t>8,37; 12,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 9,76</t>
+          <t>5,56; 9,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,91</t>
+          <t>2,73; 6,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,9</t>
+          <t>1,6; 3,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,34</t>
+          <t>6,69; 9,65</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,61</t>
+          <t>2,12; 7,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,36</t>
+          <t>1,67; 7,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,79</t>
+          <t>1,57; 5,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,56</t>
+          <t>3,69; 7,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,38</t>
+          <t>2,51; 7,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,21</t>
+          <t>3,44; 8,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,94</t>
+          <t>2,99; 7,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,42</t>
+          <t>6,7; 10,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,75</t>
+          <t>2,58; 6,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,58</t>
+          <t>3,09; 6,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,19</t>
+          <t>2,77; 6,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,74</t>
+          <t>5,89; 8,71</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,63</t>
+          <t>5,76; 7,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,93</t>
+          <t>4,37; 5,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,78</t>
+          <t>4,24; 5,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 10,98</t>
+          <t>8,57; 10,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,59; 10,59</t>
+          <t>8,64; 10,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,26</t>
+          <t>6,47; 8,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,85; 8,8</t>
+          <t>7,07; 8,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,79; 12,09</t>
+          <t>11,07; 13,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,88</t>
+          <t>7,51; 8,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,89</t>
+          <t>5,71; 6,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,15</t>
+          <t>5,88; 7,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,14</t>
+          <t>10,11; 11,61</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65807</t>
+          <t>57110</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31888</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97694</t>
+          <t>95635</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28737; 53377</t>
+          <t>30263; 53765</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28358; 51343</t>
+          <t>27882; 53409</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31791; 58384</t>
+          <t>31773; 58077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44157; 98280</t>
+          <t>37477; 83051</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41265; 67647</t>
+          <t>41058; 67362</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27698; 52160</t>
+          <t>28001; 51104</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26567; 49931</t>
+          <t>27812; 51926</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19608; 47877</t>
+          <t>24539; 57572</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78425; 112074</t>
+          <t>74524; 109951</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62038; 94815</t>
+          <t>61640; 95628</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65862; 97817</t>
+          <t>65447; 97521</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70809; 132568</t>
+          <t>71659; 126772</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49379</t>
+          <t>52418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>66178</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>109185</t>
+          <t>118596</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45545; 78128</t>
+          <t>46957; 77490</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33226; 59911</t>
+          <t>32413; 58690</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26344; 50306</t>
+          <t>27601; 51873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33809; 67319</t>
+          <t>37486; 70993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51693; 85430</t>
+          <t>51584; 83542</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39249; 67108</t>
+          <t>38846; 67588</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41913; 68911</t>
+          <t>42384; 69822</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36696; 78295</t>
+          <t>50822; 83178</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108752; 151225</t>
+          <t>106354; 150411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78658; 114736</t>
+          <t>78416; 116061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75406; 112078</t>
+          <t>77746; 115678</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81938; 134816</t>
+          <t>99050; 144916</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62807</t>
+          <t>70113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>72374</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>123994</t>
+          <t>142487</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31690; 57503</t>
+          <t>29292; 55831</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29473; 57195</t>
+          <t>30654; 56155</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22760; 45852</t>
+          <t>22134; 45531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48989; 78562</t>
+          <t>55089; 88857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>59590; 92784</t>
+          <t>58810; 91983</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60383; 95780</t>
+          <t>62036; 94351</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51521; 82386</t>
+          <t>51396; 81786</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50649; 73655</t>
+          <t>59858; 86360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97063; 141254</t>
+          <t>96747; 139681</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97968; 141613</t>
+          <t>98409; 141620</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81030; 119527</t>
+          <t>77441; 117301</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>105344; 143352</t>
+          <t>121055; 163654</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67517</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>100151</t>
+          <t>110358</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>167668</t>
+          <t>183648</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18339; 39747</t>
+          <t>18104; 41902</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8406; 26264</t>
+          <t>8371; 25481</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14130; 32773</t>
+          <t>13301; 33555</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28107; 102144</t>
+          <t>56603; 91169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38335; 67362</t>
+          <t>38279; 64409</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26900; 53277</t>
+          <t>25841; 51523</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38209; 65312</t>
+          <t>36123; 64843</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82498; 117127</t>
+          <t>94978; 127961</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61284; 99497</t>
+          <t>63131; 98310</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38886; 69338</t>
+          <t>39346; 67610</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56040; 89811</t>
+          <t>56557; 88538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>99724; 206775</t>
+          <t>160940; 207136</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43839</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>73435</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>109039</t>
+          <t>123135</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16898; 36415</t>
+          <t>16256; 35873</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8420; 23753</t>
+          <t>8445; 24418</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11421; 29855</t>
+          <t>10975; 30230</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32876; 56562</t>
+          <t>37707; 63323</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19988; 41913</t>
+          <t>19554; 41580</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12319; 30385</t>
+          <t>12545; 29450</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28820; 54199</t>
+          <t>27663; 54241</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54630; 77185</t>
+          <t>60769; 85317</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40720; 69990</t>
+          <t>41393; 69820</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24337; 48230</t>
+          <t>24104; 47601</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44605; 76316</t>
+          <t>43153; 75920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>93283; 126919</t>
+          <t>106336; 142512</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20477</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>45310</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>60142</t>
+          <t>68909</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8066; 23149</t>
+          <t>7289; 22435</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6220; 22305</t>
+          <t>6003; 23216</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1844; 10509</t>
+          <t>1811; 10261</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13856; 28431</t>
+          <t>16569; 33080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24401; 45809</t>
+          <t>24725; 46189</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8858; 24059</t>
+          <t>8815; 23916</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8004; 21799</t>
+          <t>8027; 23397</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16650; 63329</t>
+          <t>36720; 55721</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35801; 62049</t>
+          <t>35349; 61238</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18369; 39219</t>
+          <t>18100; 41338</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10873; 27786</t>
+          <t>11399; 27404</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32195; 81369</t>
+          <t>56476; 81522</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>16699</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>55701</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4022; 15978</t>
+          <t>4460; 15791</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4117; 18396</t>
+          <t>4166; 17716</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4172; 14881</t>
+          <t>4044; 15076</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10231; 21367</t>
+          <t>11435; 23965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8639; 24653</t>
+          <t>8392; 24994</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13213; 31936</t>
+          <t>13368; 33511</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12405; 31768</t>
+          <t>11973; 31093</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>27509; 44361</t>
+          <t>31105; 49052</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14820; 36724</t>
+          <t>14041; 35035</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19795; 42058</t>
+          <t>19768; 42369</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18814; 40684</t>
+          <t>18176; 41346</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>40596; 61930</t>
+          <t>45637; 67461</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>325015</t>
+          <t>342929</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>392992</t>
+          <t>445182</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>718007</t>
+          <t>788111</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>193186; 249909</t>
+          <t>188622; 250643</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>150737; 203071</t>
+          <t>149764; 203598</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>142682; 196124</t>
+          <t>143896; 193843</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>255310; 379206</t>
+          <t>302109; 386344</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>290318; 357888</t>
+          <t>291854; 358099</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>229317; 293884</t>
+          <t>230262; 293374</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>242891; 311813</t>
+          <t>250472; 315818</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>320292; 440376</t>
+          <t>411567; 484539</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>501629; 590728</t>
+          <t>499853; 593898</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>398486; 481127</t>
+          <t>398827; 481472</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>409329; 495829</t>
+          <t>408350; 493309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>623311; 790962</t>
+          <t>732522; 840964</t>
         </is>
       </c>
     </row>
